--- a/docs/billing/웰스타임_관리비_양식.xlsx
+++ b/docs/billing/웰스타임_관리비_양식.xlsx
@@ -8,25 +8,27 @@
   </bookViews>
   <sheets>
     <sheet name="관리비계산" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="원유로" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="와플칸" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="에바돈카츠" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="드림스터디" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="아기고래" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="카카오3F" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="영종스크린4F" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="코브라독스" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="미납관리" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="원유로" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="와플칸" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="에바돈카츠" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="드림스터디" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="아기고래" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="카카오3F" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="영종스크린4F" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="코브라독스" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'관리비계산'!$A$1:$O$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'원유로'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'와플칸'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'에바돈카츠'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'드림스터디'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'아기고래'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'카카오3F'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'영종스크린4F'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'코브라독스'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'미납관리'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'원유로'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'와플칸'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'에바돈카츠'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'드림스터디'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'아기고래'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'카카오3F'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'영종스크린4F'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'코브라독스'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +43,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0&quot;원/t&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +102,18 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -166,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -227,6 +241,16 @@
     <xf numFmtId="166" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,8 +1053,9 @@
         <f>E14+F14+G14+H14+I14+J14</f>
         <v/>
       </c>
-      <c r="L14" s="6" t="n">
-        <v>0</v>
+      <c r="L14" s="13">
+        <f>미납관리!B6</f>
+        <v/>
       </c>
       <c r="M14" s="13">
         <f>ROUND(L14*$I$8,0)</f>
@@ -1089,8 +1114,9 @@
         <f>E15+F15+G15+H15+I15+J15</f>
         <v/>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
+      <c r="L15" s="13">
+        <f>미납관리!B7</f>
+        <v/>
       </c>
       <c r="M15" s="13">
         <f>ROUND(L15*$I$8,0)</f>
@@ -1149,8 +1175,9 @@
         <f>E16+F16+G16+H16+I16+J16</f>
         <v/>
       </c>
-      <c r="L16" s="6" t="n">
-        <v>0</v>
+      <c r="L16" s="13">
+        <f>미납관리!B8</f>
+        <v/>
       </c>
       <c r="M16" s="13">
         <f>ROUND(L16*$I$8,0)</f>
@@ -1209,8 +1236,9 @@
         <f>E17+F17+G17+H17+I17+J17</f>
         <v/>
       </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
+      <c r="L17" s="13">
+        <f>미납관리!B9</f>
+        <v/>
       </c>
       <c r="M17" s="13">
         <f>ROUND(L17*$I$8,0)</f>
@@ -1269,8 +1297,9 @@
         <f>E18+F18+G18+H18+I18+J18</f>
         <v/>
       </c>
-      <c r="L18" s="6" t="n">
-        <v>0</v>
+      <c r="L18" s="13">
+        <f>미납관리!B10</f>
+        <v/>
       </c>
       <c r="M18" s="13">
         <f>ROUND(L18*$I$8,0)</f>
@@ -1329,8 +1358,9 @@
         <f>E19+F19+G19+H19+I19+J19</f>
         <v/>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
+      <c r="L19" s="13">
+        <f>미납관리!B11</f>
+        <v/>
       </c>
       <c r="M19" s="13">
         <f>ROUND(L19*$I$8,0)</f>
@@ -1389,8 +1419,9 @@
         <f>E20+F20+G20+H20+I20+J20</f>
         <v/>
       </c>
-      <c r="L20" s="6" t="n">
-        <v>0</v>
+      <c r="L20" s="13">
+        <f>미납관리!B12</f>
+        <v/>
       </c>
       <c r="M20" s="13">
         <f>ROUND(L20*$I$8,0)</f>
@@ -1449,8 +1480,9 @@
         <f>E21+F21+G21+H21+I21+J21</f>
         <v/>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
+      <c r="L21" s="13">
+        <f>미납관리!B13</f>
+        <v/>
       </c>
       <c r="M21" s="13">
         <f>ROUND(L21*$I$8,0)</f>
@@ -1589,7 +1621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1605,167 +1637,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>원유로 (105호)</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>코브라독스</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H14</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H21</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I14</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I21</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J14</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J21</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E14</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E21</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F14</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F21</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G14</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G21</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K14</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K21</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L14</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L21</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M14</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M21</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N14</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N21</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O14</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O21</f>
         <v/>
       </c>
     </row>
@@ -1784,7 +1816,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -1801,6 +1833,371 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>미납 관리 (누적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>노란칸(전월 이월미납액·이번달 납부액)만 입력. '전월 이월미납액'은 청구서 미납액으로 자동 연결됩니다. 다음 달엔 '이번달말 미납잔액'을 다음 달의 '전월 이월'에 옮겨 적으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>연체료는 전월 이월미납액에 1.5% 한 번만 부과(청구서에 반영). 원금(미납잔액)에는 더하지 않아 매월 누적·복리되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>세대명</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>전월 이월미납액</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>미납연체료(1.5%)</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>이번달 당월부과액</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>이번달 납부액</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>이번달말 미납잔액</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>원유로</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <f>ROUND(B6*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="13">
+        <f>관리비계산!K14</f>
+        <v/>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18">
+        <f>B6+D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="24" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>와플칸</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13">
+        <f>ROUND(B7*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="13">
+        <f>관리비계산!K15</f>
+        <v/>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <f>B7+D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="24" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>에바돈카츠</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <f>ROUND(B8*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>관리비계산!K16</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <f>B8+D8-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="24" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>드림스터디</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>5470868</v>
+      </c>
+      <c r="C9" s="13">
+        <f>ROUND(B9*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>관리비계산!K17</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18">
+        <f>B9+D9-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>원본 6월 기준 예시-확인 후 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>아기고래</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <f>ROUND(B10*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>관리비계산!K18</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <f>B10+D10-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="24" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>카카오3F</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13">
+        <f>ROUND(B11*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>관리비계산!K19</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <f>B11+D11-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="24" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>영종스크린4F</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <f>ROUND(B12*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
+        <f>관리비계산!K20</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <f>B12+D12-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="24" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>코브라독스</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13">
+        <f>ROUND(B13*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>관리비계산!K21</f>
+        <v/>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <f>B13+D13-E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>명성화로(퇴거)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>6635886</v>
+      </c>
+      <c r="C14" s="13">
+        <f>ROUND(B14*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <f>B14+D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>퇴거 미수금-원본 6월 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>합 계</t>
+        </is>
+      </c>
+      <c r="B15" s="20">
+        <f>SUM(B6:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>SUM(C6:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>SUM(D6:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>SUM(E6:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>SUM(F6:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B6:B14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="0 이상의 숫자를 입력하세요." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6:E14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="0 이상의 숫자를 입력하세요." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1820,167 +2217,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>와플칸</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>원유로 (105호)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H15</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H14</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I15</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I14</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J15</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J14</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E15</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E14</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F15</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F14</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G15</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G14</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K15</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L15</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M15</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M14</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N15</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N14</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O15</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O14</f>
         <v/>
       </c>
     </row>
@@ -1999,7 +2396,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -2035,167 +2432,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>에바돈카츠</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>와플칸</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H16</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H15</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I16</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I15</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J16</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J15</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E16</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E15</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F16</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F15</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G16</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G15</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K16</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K15</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L16</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M16</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N16</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O16</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O15</f>
         <v/>
       </c>
     </row>
@@ -2214,7 +2611,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -2250,167 +2647,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>드림스터디</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>에바돈카츠</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H17</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H16</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I17</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I16</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J17</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J16</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E17</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E16</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F17</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F16</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G17</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G16</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K17</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K16</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L17</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L16</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M17</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N17</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N16</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O17</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O16</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2826,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -2465,167 +2862,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>아기고래</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>드림스터디</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H18</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H17</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I18</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I17</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J18</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J17</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E18</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E17</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F18</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F17</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G18</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G17</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K18</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K17</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L18</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L17</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M18</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M17</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N18</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O18</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O17</f>
         <v/>
       </c>
     </row>
@@ -2644,7 +3041,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -2680,167 +3077,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>카카오3F</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>아기고래</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H19</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H18</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I19</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I18</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J19</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J18</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E19</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E18</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F19</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F18</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G19</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G18</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K19</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K18</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L19</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L18</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M19</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M18</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N19</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N18</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O19</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O18</f>
         <v/>
       </c>
     </row>
@@ -2859,7 +3256,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -2895,167 +3292,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>영종스크린4F</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>카카오3F</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H20</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H19</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I20</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I19</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J20</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J19</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E20</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E19</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F20</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F19</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G20</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G19</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K20</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K19</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L20</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L19</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M20</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M19</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N20</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N19</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O20</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O19</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3471,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>
@@ -3110,167 +3507,167 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>관 리 비 청 구 서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>웰스타임 관리사무소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <f>관리비계산!B5&amp;"년 "&amp;관리비계산!D5&amp;"월분"</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>세대명</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>코브라독스</t>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>영종스크린4F</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일반관리비</t>
         </is>
       </c>
-      <c r="C8" s="29">
-        <f>관리비계산!H21</f>
+      <c r="C8" s="33">
+        <f>관리비계산!H20</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>관리비 부가세</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>관리비계산!I21</f>
+      <c r="C9" s="33">
+        <f>관리비계산!I20</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>청소비품</t>
         </is>
       </c>
-      <c r="C10" s="29">
-        <f>관리비계산!J21</f>
+      <c r="C10" s="33">
+        <f>관리비계산!J20</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>세대 상수도료</t>
         </is>
       </c>
-      <c r="C11" s="29">
-        <f>관리비계산!E21</f>
+      <c r="C11" s="33">
+        <f>관리비계산!E20</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>공동 수도료</t>
         </is>
       </c>
-      <c r="C12" s="29">
-        <f>관리비계산!F21</f>
+      <c r="C12" s="33">
+        <f>관리비계산!F20</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>전기료(공용)</t>
         </is>
       </c>
-      <c r="C13" s="29">
-        <f>관리비계산!G21</f>
+      <c r="C13" s="33">
+        <f>관리비계산!G20</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>당월부과액 계</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>관리비계산!K21</f>
+      <c r="C14" s="35">
+        <f>관리비계산!K20</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>전월 미납액</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>관리비계산!L21</f>
+      <c r="C15" s="33">
+        <f>관리비계산!L20</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>미납 연체료(1.5%)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>관리비계산!M21</f>
+      <c r="C16" s="33">
+        <f>관리비계산!M20</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>납기내 금액</t>
         </is>
       </c>
-      <c r="C17" s="33">
-        <f>관리비계산!N21</f>
+      <c r="C17" s="37">
+        <f>관리비계산!N20</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>납기후 금액</t>
         </is>
       </c>
-      <c r="C18" s="35">
-        <f>관리비계산!O21</f>
+      <c r="C18" s="39">
+        <f>관리비계산!O20</f>
         <v/>
       </c>
     </row>
@@ -3289,7 +3686,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>위 금액을 청구합니다.  웰스타임 관리사무소</t>
         </is>

--- a/docs/billing/웰스타임_관리비_양식.xlsx
+++ b/docs/billing/웰스타임_관리비_양식.xlsx
@@ -1066,7 +1066,7 @@
         <v/>
       </c>
       <c r="O14" s="18">
-        <f>ROUND(N14*(1+$I$8),0)</f>
+        <f>N14+ROUND(K14*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="O15" s="18">
-        <f>ROUND(N15*(1+$I$8),0)</f>
+        <f>N15+ROUND(K15*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="O16" s="18">
-        <f>ROUND(N16*(1+$I$8),0)</f>
+        <f>N16+ROUND(K16*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="O17" s="18">
-        <f>ROUND(N17*(1+$I$8),0)</f>
+        <f>N17+ROUND(K17*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="O18" s="18">
-        <f>ROUND(N18*(1+$I$8),0)</f>
+        <f>N18+ROUND(K18*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v/>
       </c>
       <c r="O19" s="18">
-        <f>ROUND(N19*(1+$I$8),0)</f>
+        <f>N19+ROUND(K19*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
       <c r="O20" s="18">
-        <f>ROUND(N20*(1+$I$8),0)</f>
+        <f>N20+ROUND(K20*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v/>
       </c>
       <c r="O21" s="18">
-        <f>ROUND(N21*(1+$I$8),0)</f>
+        <f>N21+ROUND(K21*$I$8,0)</f>
         <v/>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <f>ROUND(B6*0.015,0)</f>
+        <f>ROUND(B6*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D6" s="13">
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="13">
-        <f>ROUND(B7*0.015,0)</f>
+        <f>ROUND(B7*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D7" s="13">
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="13">
-        <f>ROUND(B8*0.015,0)</f>
+        <f>ROUND(B8*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D8" s="13">
@@ -2001,7 +2001,7 @@
         <v>5470868</v>
       </c>
       <c r="C9" s="13">
-        <f>ROUND(B9*0.015,0)</f>
+        <f>ROUND(B9*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D9" s="13">
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="13">
-        <f>ROUND(B10*0.015,0)</f>
+        <f>ROUND(B10*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D10" s="13">
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="13">
-        <f>ROUND(B11*0.015,0)</f>
+        <f>ROUND(B11*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D11" s="13">
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="13">
-        <f>ROUND(B12*0.015,0)</f>
+        <f>ROUND(B12*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D12" s="13">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="13">
-        <f>ROUND(B13*0.015,0)</f>
+        <f>ROUND(B13*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D13" s="13">
@@ -2135,7 +2135,7 @@
         <v>6635886</v>
       </c>
       <c r="C14" s="13">
-        <f>ROUND(B14*0.015,0)</f>
+        <f>ROUND(B14*관리비계산!$I$8,0)</f>
         <v/>
       </c>
       <c r="D14" s="13" t="n">

--- a/docs/billing/웰스타임_관리비_양식.xlsx
+++ b/docs/billing/웰스타임_관리비_양식.xlsx
@@ -154,7 +154,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -176,11 +176,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -292,6 +336,8 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -700,7 +746,6 @@
           <t>노란칸(  )에만 매달 숫자를 입력하세요. 파란칸은 자동으로 계산됩니다.</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -744,7 +789,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -752,7 +797,7 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>760500</v>
+        <v>960100</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -787,13 +832,11 @@
       <c r="C7" s="6" t="n">
         <v>203280</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>전기(전력량)요금</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>203280</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>439160</v>
+        <v>562270</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -801,7 +844,7 @@
         </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>15760</v>
+        <v>18790</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -810,7 +853,7 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>05.04-06.03</t>
+          <t>06.04-07.03</t>
         </is>
       </c>
     </row>
@@ -901,11 +944,15 @@
           <t>세대 정보</t>
         </is>
       </c>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="42" t="n"/>
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>수  도</t>
         </is>
       </c>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="42" t="n"/>
       <c r="G12" s="15" t="inlineStr">
         <is>
           <t>전기</t>
@@ -916,6 +963,8 @@
           <t>일반 관리비</t>
         </is>
       </c>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="42" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>당월</t>
@@ -926,11 +975,13 @@
           <t>미납·연체</t>
         </is>
       </c>
+      <c r="M12" s="42" t="n"/>
       <c r="N12" s="15" t="inlineStr">
         <is>
           <t>청구 금액</t>
         </is>
       </c>
+      <c r="O12" s="42" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -1023,7 +1074,7 @@
         <v/>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E14" s="13">
         <f>ROUND($C$10*D14,0)</f>
@@ -1084,7 +1135,7 @@
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E15" s="13">
         <f>ROUND($C$10*D15,0)</f>
@@ -1145,7 +1196,7 @@
         <v/>
       </c>
       <c r="D16" s="8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E16" s="13">
         <f>ROUND($C$10*D16,0)</f>
@@ -1206,7 +1257,7 @@
         <v/>
       </c>
       <c r="D17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="13">
         <f>ROUND($C$10*D17,0)</f>
@@ -1267,7 +1318,7 @@
         <v/>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" s="13">
         <f>ROUND($C$10*D18,0)</f>
@@ -1328,7 +1379,7 @@
         <v/>
       </c>
       <c r="D19" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="13">
         <f>ROUND($C$10*D19,0)</f>
